--- a/prompts.xlsx
+++ b/prompts.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario1\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario1\Documents\mestrado\ia\at1-4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F80C85B-DB70-4643-9F6B-6C6A6A33123C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF76AC5D-E574-4059-A2BA-BAB2A9AF6624}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="26">
   <si>
     <t>Model Name and Version - Agent Name - Skills and Agents</t>
   </si>
@@ -64,6 +64,67 @@
   </si>
   <si>
     <t>Ruim</t>
+  </si>
+  <si>
+    <t>O agente criou as pastas mas não criou o sistema react</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> vamos para o segundo requisito: 2. Gerenciamento (inclusão, alteração e remoção) de provas. Cada prova é criada a
+  partir da
+  seleção de um conjunto de questões previamente cadastradas no sistema. O usuário deve
+  informar se, para a prova sendo criada, as alternativas das questões devem ser identificadas
+  por letras ou por potências de 2 (1, 2, 4, 8, 16, 32,…). No caso de letras, deve haver espaço
+  após a questão para que o aluno indique as letras marcadas. No caso das potências, deve
+  haver espaço para o aluno indicar a soma das alternativas marcadas pelo aluno.</t>
+  </si>
+  <si>
+    <t>Nenhum</t>
+  </si>
+  <si>
+    <t>Ok</t>
+  </si>
+  <si>
+    <t>O agente criou o requisito da forma correta</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> agora vamos implementar o terceiro requisito: 3. Geração dos PDFs de um número (fornecido pelo usuário) de provas
+  individuais, variando a
+  ordem em que as questões e as alternativas aparecem em cada prova. Cada PDF deve ter o
+  cabeçalho da prova (com nome da disciplina, professor, data, etc.). Cada página da prova
+  deve ter com rodapé o número da prova individual gerada pelo sistema. No final do PDF,
+  deve ter espaço para o aluno informar seu nome e CPF). O sistema deve gerar também um
+  CSV com o gabarito de cada prova. Cada linha do CSV contém informações sobre uma
+  prova: o número da prova, seguido do gabarito de cada questão da prova (as letras que
+  deveriam ser selecionadas, ou o somatório esperado). </t>
+  </si>
+  <si>
+    <t>A geração dos pdfs está com erro</t>
+  </si>
+  <si>
+    <t>Essa abordagem funcionou nas outras abordagens, mas não nessa</t>
+  </si>
+  <si>
+    <t>Gerou codigo duplicado</t>
+  </si>
+  <si>
+    <t>Corrija a geração dos pdfs</t>
+  </si>
+  <si>
+    <t>OK</t>
+  </si>
+  <si>
+    <t>Dessa vez gerou o pdf de forma correta</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> agora vamos para o ultimo requisito: 4. Por fim, o sistema deve permitir a correção das provas e a geração do
+  relatório de notas da
+  turma. Para corrigir a prova, deve-se informar ao sistema o CSV com o gabarito e outro
+  CSV com as respostas informadas pelo aluno (normalmente através de um google forms que
+  coleta o número da prova e a resposta dada pelo aluno para cada questão). A prova deve ser
+  corrigida de forma mais (uma alternativa que incorretamente foi selecionada ou deixada de
+  ser selecionada zera toda a questão) ou menos (a nota da questão é proporcional ao
+  percentual de alternativas selecionadas ou deixadas de ser selecionadas incorretamente)
+  rigorosa. </t>
   </si>
 </sst>
 </file>
@@ -1517,32 +1578,68 @@
       <c r="C4" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-    </row>
-    <row r="5" spans="1:5" ht="20.100000000000001" customHeight="1">
-      <c r="A5" s="7"/>
-      <c r="B5" s="8"/>
-      <c r="C5" s="9"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
-    </row>
-    <row r="6" spans="1:5" ht="20.100000000000001" customHeight="1">
-      <c r="A6" s="7"/>
-      <c r="B6" s="8"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
-    </row>
-    <row r="7" spans="1:5" ht="20.100000000000001" customHeight="1">
-      <c r="A7" s="7"/>
-      <c r="B7" s="8"/>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
-    </row>
-    <row r="8" spans="1:5" ht="20.100000000000001" customHeight="1">
-      <c r="A8" s="7"/>
+      <c r="D4" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="184.8">
+      <c r="A5" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="237.6">
+      <c r="A6" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="26.4">
+      <c r="A7" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="224.4">
+      <c r="A8" s="7" t="s">
+        <v>25</v>
+      </c>
       <c r="B8" s="8"/>
       <c r="C8" s="9"/>
       <c r="D8" s="9"/>

--- a/prompts.xlsx
+++ b/prompts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario1\Documents\mestrado\ia\at1-4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF76AC5D-E574-4059-A2BA-BAB2A9AF6624}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7192AF4C-20E2-4C5B-B3AF-06F9E1D4D8E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="33">
   <si>
     <t>Model Name and Version - Agent Name - Skills and Agents</t>
   </si>
@@ -126,12 +126,33 @@
   percentual de alternativas selecionadas ou deixadas de ser selecionadas incorretamente)
   rigorosa. </t>
   </si>
+  <si>
+    <t>A correção não está funcionando bem</t>
+  </si>
+  <si>
+    <t>mais ou menos</t>
+  </si>
+  <si>
+    <t>Crie uma opção para gerar um arquivo csv com as respostas da prova</t>
+  </si>
+  <si>
+    <t>O codigo gerado não funcionou</t>
+  </si>
+  <si>
+    <t>Ele gerou o codigo mas não funcionou</t>
+  </si>
+  <si>
+    <t>Corrija a geração das respostas</t>
+  </si>
+  <si>
+    <t>Dessa vez ele corrigiu e funciona de forma correta</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="10"/>
       <color indexed="8"/>
@@ -151,6 +172,12 @@
     <font>
       <b/>
       <i/>
+      <sz val="10"/>
+      <color indexed="8"/>
+      <name val="Helvetica Neue"/>
+    </font>
+    <font>
+      <u/>
       <sz val="10"/>
       <color indexed="8"/>
       <name val="Helvetica Neue"/>
@@ -338,7 +365,7 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -383,6 +410,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1517,7 +1547,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E63"/>
+  <dimension ref="A1:G63"/>
   <sheetFormatPr defaultColWidth="16.33203125" defaultRowHeight="19.95" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="44.33203125" style="1" customWidth="1"/>
@@ -1527,7 +1557,7 @@
     <col min="7" max="16384" width="16.33203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="27.6" customHeight="1">
+    <row r="1" spans="1:7" ht="27.6" customHeight="1">
       <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
@@ -1536,7 +1566,7 @@
       <c r="D1" s="13"/>
       <c r="E1" s="14"/>
     </row>
-    <row r="2" spans="1:5" ht="20.25" customHeight="1">
+    <row r="2" spans="1:7" ht="20.25" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -1553,7 +1583,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="105.6">
+    <row r="3" spans="1:7" ht="105.6">
       <c r="A3" s="4" t="s">
         <v>6</v>
       </c>
@@ -1568,7 +1598,7 @@
       </c>
       <c r="E3" s="6"/>
     </row>
-    <row r="4" spans="1:5" ht="92.4">
+    <row r="4" spans="1:7" ht="92.4">
       <c r="A4" s="7" t="s">
         <v>7</v>
       </c>
@@ -1585,7 +1615,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="184.8">
+    <row r="5" spans="1:7" ht="184.8">
       <c r="A5" s="7" t="s">
         <v>14</v>
       </c>
@@ -1602,7 +1632,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="237.6">
+    <row r="6" spans="1:7" ht="237.6">
       <c r="A6" s="7" t="s">
         <v>18</v>
       </c>
@@ -1619,7 +1649,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="26.4">
+    <row r="7" spans="1:7" ht="26.4">
       <c r="A7" s="7" t="s">
         <v>22</v>
       </c>
@@ -1636,65 +1666,92 @@
         <v>24</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="224.4">
+    <row r="8" spans="1:7" ht="224.4">
       <c r="A8" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="B8" s="8"/>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
+      <c r="B8" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>10</v>
+      </c>
       <c r="E8" s="9"/>
-    </row>
-    <row r="9" spans="1:5" ht="20.100000000000001" customHeight="1">
-      <c r="A9" s="7"/>
-      <c r="B9" s="8"/>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-    </row>
-    <row r="10" spans="1:5" ht="20.100000000000001" customHeight="1">
-      <c r="A10" s="7"/>
-      <c r="B10" s="8"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-    </row>
-    <row r="11" spans="1:5" ht="20.100000000000001" customHeight="1">
+      <c r="G8" s="15"/>
+    </row>
+    <row r="9" spans="1:7" ht="26.4">
+      <c r="A9" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="26.4">
+      <c r="A10" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="20.100000000000001" customHeight="1">
       <c r="A11" s="7"/>
       <c r="B11" s="8"/>
       <c r="C11" s="9"/>
       <c r="D11" s="9"/>
       <c r="E11" s="9"/>
     </row>
-    <row r="12" spans="1:5" ht="20.100000000000001" customHeight="1">
+    <row r="12" spans="1:7" ht="20.100000000000001" customHeight="1">
       <c r="A12" s="7"/>
       <c r="B12" s="8"/>
       <c r="C12" s="9"/>
       <c r="D12" s="9"/>
       <c r="E12" s="9"/>
     </row>
-    <row r="13" spans="1:5" ht="20.100000000000001" customHeight="1">
+    <row r="13" spans="1:7" ht="20.100000000000001" customHeight="1">
       <c r="A13" s="7"/>
       <c r="B13" s="8"/>
       <c r="C13" s="9"/>
       <c r="D13" s="9"/>
       <c r="E13" s="9"/>
     </row>
-    <row r="14" spans="1:5" ht="20.100000000000001" customHeight="1">
+    <row r="14" spans="1:7" ht="20.100000000000001" customHeight="1">
       <c r="A14" s="7"/>
       <c r="B14" s="8"/>
       <c r="C14" s="9"/>
       <c r="D14" s="9"/>
       <c r="E14" s="9"/>
     </row>
-    <row r="15" spans="1:5" ht="20.100000000000001" customHeight="1">
+    <row r="15" spans="1:7" ht="20.100000000000001" customHeight="1">
       <c r="A15" s="7"/>
       <c r="B15" s="8"/>
       <c r="C15" s="9"/>
       <c r="D15" s="9"/>
       <c r="E15" s="9"/>
     </row>
-    <row r="16" spans="1:5" ht="20.100000000000001" customHeight="1">
+    <row r="16" spans="1:7" ht="20.100000000000001" customHeight="1">
       <c r="A16" s="7"/>
       <c r="B16" s="8"/>
       <c r="C16" s="9"/>

--- a/prompts.xlsx
+++ b/prompts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario1\Documents\mestrado\ia\at1-4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7192AF4C-20E2-4C5B-B3AF-06F9E1D4D8E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6E84469-F7BD-4ADC-A746-B5714CE5032A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="35">
   <si>
     <t>Model Name and Version - Agent Name - Skills and Agents</t>
   </si>
@@ -146,6 +146,13 @@
   </si>
   <si>
     <t>Dessa vez ele corrigiu e funciona de forma correta</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> agora vamos criar os testes,  use a linguagem Gherkin do Cucumber, que deve ser usado para 
+  implementar os testes de aceitação.</t>
+  </si>
+  <si>
+    <t>Criou os testes</t>
   </si>
 </sst>
 </file>
@@ -402,6 +409,9 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -410,9 +420,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1558,13 +1565,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="27.6" customHeight="1">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="14"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="15"/>
     </row>
     <row r="2" spans="1:7" ht="20.25" customHeight="1">
       <c r="A2" s="2" t="s">
@@ -1680,7 +1687,7 @@
         <v>10</v>
       </c>
       <c r="E8" s="9"/>
-      <c r="G8" s="15"/>
+      <c r="G8" s="12"/>
     </row>
     <row r="9" spans="1:7" ht="26.4">
       <c r="A9" s="7" t="s">
@@ -1716,12 +1723,22 @@
         <v>32</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="20.100000000000001" customHeight="1">
-      <c r="A11" s="7"/>
-      <c r="B11" s="8"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
+    <row r="11" spans="1:7" ht="39.6">
+      <c r="A11" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="12" spans="1:7" ht="20.100000000000001" customHeight="1">
       <c r="A12" s="7"/>
